--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:00</t>
+    <t xml:space="preserve">2026-09-10 01:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:11</t>
+    <t xml:space="preserve">2026-09-12 22:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:23</t>
+    <t xml:space="preserve">2026-09-23 23:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:52</t>
+    <t xml:space="preserve">2026-10-02 16:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:00</t>
+    <t xml:space="preserve">2026-10-05 16:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
